--- a/data/b2_candoi/B2 Candói 06-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 06-2026.xlsx
@@ -4793,56 +4793,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2210.43</v>
+        <v>1336.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>56291.44</v>
+        <v>2488.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46180</v>
+        <v>46178</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>850.58</v>
+        <v>58144.46</v>
       </c>
     </row>
     <row r="5">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3616.76</v>
+        <v>3897.31</v>
       </c>
     </row>
     <row r="6">
@@ -4869,39 +4869,39 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3200</v>
+        <v>2717.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>984.1900000000001</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46186</v>
+        <v>46184</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -4910,47 +4910,47 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1151.51</v>
+        <v>996.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46187</v>
+        <v>46185</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>3390.94</v>
+        <v>1004.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>8240.940000000001</v>
+        <v>3615.47</v>
       </c>
     </row>
     <row r="11">
@@ -4959,16 +4959,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1332.88</v>
+        <v>8457.27</v>
       </c>
     </row>
     <row r="12">
@@ -4986,79 +4986,79 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>877.8099999999999</v>
+        <v>1067.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Reforma dos banheiros</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1069.46</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Reforma dos banheiros</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>7600</v>
+        <v>20126.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20155.4</v>
+        <v>3554.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46194</v>
+        <v>46198</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3656.08</v>
+        <v>8910</v>
       </c>
     </row>
     <row r="17">
@@ -5067,16 +5067,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>8910</v>
+        <v>1018.99</v>
       </c>
     </row>
     <row r="18">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3833.95</v>
+        <v>3530.65</v>
       </c>
     </row>
     <row r="19">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>980.02</v>
+        <v>1036.2</v>
       </c>
     </row>
   </sheetData>
